--- a/Stundenliste(1).xlsx
+++ b/Stundenliste(1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VR1\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linus.pilz\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6396F35-D50D-42BC-8F79-3308837EFFD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7892893B-8816-4356-95B0-22028287196E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="20625" xr2:uid="{904973F5-B02B-4666-A03D-BB66738E721E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{904973F5-B02B-4666-A03D-BB66738E721E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -34,12 +34,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="50">
   <si>
     <t>Tag</t>
   </si>
@@ -162,21 +165,49 @@
   </si>
   <si>
     <t>Ausprobieren der Haptik-Weste</t>
+  </si>
+  <si>
+    <t>Minuten</t>
+  </si>
+  <si>
+    <t>Stunden2</t>
+  </si>
+  <si>
+    <t>Prozent</t>
+  </si>
+  <si>
+    <t>Github in Word beschrieben</t>
+  </si>
+  <si>
+    <t>Allgemeinen Funktionen von Github in Word</t>
+  </si>
+  <si>
+    <t>Miteinander Word geschrieben</t>
+  </si>
+  <si>
+    <t>Informatik Stundenliste verbessert</t>
+  </si>
+  <si>
+    <t>Alles</t>
+  </si>
+  <si>
+    <t>Spalte1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="h:m"/>
     <numFmt numFmtId="165" formatCode="h:mm"/>
     <numFmt numFmtId="166" formatCode="[hh]:mm"/>
     <numFmt numFmtId="167" formatCode="#,##0.00\ _€"/>
     <numFmt numFmtId="168" formatCode="0.00&quot; Stunden&quot;"/>
     <numFmt numFmtId="169" formatCode="0.00&quot; h&quot;"/>
+    <numFmt numFmtId="170" formatCode="[mm]"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,6 +232,13 @@
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -249,10 +287,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -282,11 +321,101 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="46" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Prozent" xfId="1" builtinId="5"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="17">
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[mm]"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[mm]"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[hh]:mm"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="[hh]:mm"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -300,19 +429,6 @@
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="164" formatCode="h:m"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -409,65 +525,6 @@
         <scheme val="minor"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="[hh]:mm"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[hh]:mm"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -486,6 +543,1278 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="de-DE"/>
+              <a:t>Stunden in Prozent</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$L$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Linus</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="de-DE"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$Q$3</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.54002192982455854</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-261E-4EBB-BB6E-D2A68DA9809C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$L$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Arthur</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="de-DE"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$Q$4</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.37646198830409167</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-261E-4EBB-BB6E-D2A68DA9809C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$L$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Valentin</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="de-DE"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$Q$5</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.44407894736841874</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-261E-4EBB-BB6E-D2A68DA9809C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$L$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Alles</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="de-DE"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$Q$6</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-261E-4EBB-BB6E-D2A68DA9809C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="1163337359"/>
+        <c:axId val="1163341679"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1163337359"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1163341679"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1163341679"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1163337359"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>12417</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>185057</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>70757</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Diagramm 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD40C3BE-BAD2-C4CC-7264-122DAE0FD575}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -494,54 +1823,68 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Tabelle1"/>
+      <sheetName val="Stundenliste"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD71F5EC-BCBD-4D95-9F21-060EF7779827}" name="Stundenliste" displayName="Stundenliste" ref="A1:G41" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD71F5EC-BCBD-4D95-9F21-060EF7779827}" name="Stundenliste" displayName="Stundenliste" ref="A1:G41" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
   <autoFilter ref="A1:G41" xr:uid="{730AE997-56E9-481C-8C9C-45C7D9E3EFFC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G41">
     <sortCondition ref="B1:B41"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{AD59871A-76CC-45F6-8F91-44F7ED02573E}" name="Tag" dataDxfId="6">
+    <tableColumn id="1" xr3:uid="{AD59871A-76CC-45F6-8F91-44F7ED02573E}" name="Tag" dataDxfId="14">
       <calculatedColumnFormula>IF(ISNUMBER(B2),LEFT(TEXT(B2,"TTTT"),2)&amp;".","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0BE9BF18-BC7D-4870-8E1C-AF08893F5227}" name="Datum" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{8264A4E0-F28F-4A0D-A490-C90DCCB13F8E}" name="Tätigkeit/Info" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{FE347096-2316-4A4F-8E95-6B08EDE9030A}" name="Von" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{DF9965FF-51AE-44CD-90F9-60C1127D4458}" name="Bis" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{71889B4E-2C0D-4CC7-AB39-54AAA30FF7DC}" name="Stunden" dataDxfId="0">
+    <tableColumn id="2" xr3:uid="{0BE9BF18-BC7D-4870-8E1C-AF08893F5227}" name="Datum" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{8264A4E0-F28F-4A0D-A490-C90DCCB13F8E}" name="Tätigkeit/Info" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{FE347096-2316-4A4F-8E95-6B08EDE9030A}" name="Von" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{DF9965FF-51AE-44CD-90F9-60C1127D4458}" name="Bis" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{71889B4E-2C0D-4CC7-AB39-54AAA30FF7DC}" name="Stunden" dataDxfId="9">
       <calculatedColumnFormula>IF(E2&gt;D2,E2-D2,IF(ISNUMBER([1]!Stundenliste[[#This Row],[Von]]),"24:00"-(D2-E2),""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{37DB6F7E-AF9C-40D4-A31C-91C6CFAF5E2F}" name="Wer" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{37DB6F7E-AF9C-40D4-A31C-91C6CFAF5E2F}" name="Wer" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{028D3482-62D4-45D7-85FA-8EC2E4DDD78D}" name="Tabelle2" displayName="Tabelle2" ref="L2:M5" totalsRowShown="0">
-  <autoFilter ref="L2:M5" xr:uid="{028D3482-62D4-45D7-85FA-8EC2E4DDD78D}"/>
-  <tableColumns count="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{028D3482-62D4-45D7-85FA-8EC2E4DDD78D}" name="Tabelle2" displayName="Tabelle2" ref="L2:Q6" totalsRowShown="0">
+  <autoFilter ref="L2:Q6" xr:uid="{028D3482-62D4-45D7-85FA-8EC2E4DDD78D}"/>
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9B6AAEA3-668A-4353-A33E-0D79279FD064}" name="Name"/>
-    <tableColumn id="2" xr3:uid="{DF593358-143C-4B61-887F-2E7A8967BB61}" name="Stunden" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{DF593358-143C-4B61-887F-2E7A8967BB61}" name="Stunden" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{48C02AA9-4970-411A-A4BA-20AFF4C20E61}" name="Minuten" dataDxfId="3">
+      <calculatedColumnFormula>Tabelle2[[#This Row],[Stunden]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{FBD2B55A-1785-4AEE-A362-0CDA5F4271CA}" name="Stunden2" dataDxfId="2">
+      <calculatedColumnFormula>Tabelle2[[#This Row],[Minuten]]/60</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{43C88CC5-3A35-4698-8EA5-94C339438E12}" name="Prozent" dataDxfId="1">
+      <calculatedColumnFormula>(O3/180)*100</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{6AA6588C-B2BB-4A64-8166-D31634AA0806}" name="Spalte1" dataDxfId="0">
+      <calculatedColumnFormula>P3*1421.05263157894</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8B5F2195-23C3-4CB7-A5D3-21B8075D8571}" name="Tabelle5" displayName="Tabelle5" ref="I2:J11" totalsRowShown="0" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8B5F2195-23C3-4CB7-A5D3-21B8075D8571}" name="Tabelle5" displayName="Tabelle5" ref="I2:J11" totalsRowShown="0" dataDxfId="7">
   <autoFilter ref="I2:J11" xr:uid="{8B5F2195-23C3-4CB7-A5D3-21B8075D8571}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{5F655F81-B105-43EE-8AB9-3B34703E1464}" name="Name" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{B0F8400B-CC18-431B-B826-95EE145FC5C8}" name="Zeit" dataDxfId="9">
+    <tableColumn id="1" xr3:uid="{5F655F81-B105-43EE-8AB9-3B34703E1464}" name="Name" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{B0F8400B-CC18-431B-B826-95EE145FC5C8}" name="Zeit" dataDxfId="5">
       <calculatedColumnFormula>SUMIF(Stundenliste[Wer],I3,Stundenliste[Stunden])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -847,7 +2190,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{730198CE-52B5-4F02-9B4B-1774B163D30B}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:Q41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -859,7 +2202,7 @@
     <col min="7" max="7" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -882,9 +2225,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="str">
-        <f>IF(ISNUMBER(B2),LEFT(TEXT(B2,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" ref="A2:A34" si="0">IF(ISNUMBER(B2),LEFT(TEXT(B2,"TTTT"),2)&amp;".","")</f>
         <v>So.</v>
       </c>
       <c r="B2" s="3">
@@ -918,10 +2261,22 @@
       <c r="M2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N2" t="s">
+        <v>41</v>
+      </c>
+      <c r="O2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="str">
-        <f>IF(ISNUMBER(B3),LEFT(TEXT(B3,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Di.</v>
       </c>
       <c r="B3" s="3">
@@ -956,12 +2311,28 @@
       </c>
       <c r="M3" s="11">
         <f>SUM(J4,J7,J8,J11)</f>
-        <v>3.729166666666667</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+        <v>4.1041666666666661</v>
+      </c>
+      <c r="N3" s="19">
+        <f>M3</f>
+        <v>4.1041666666666661</v>
+      </c>
+      <c r="O3" s="19">
+        <f>N3/60</f>
+        <v>6.8402777777777771E-2</v>
+      </c>
+      <c r="P3" s="23">
+        <f t="shared" ref="P3:P6" si="1">(O3/180)*100</f>
+        <v>3.8001543209876538E-2</v>
+      </c>
+      <c r="Q3" s="22">
+        <f>(P3*1421.05263157894)/100</f>
+        <v>0.54002192982455854</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="str">
-        <f>IF(ISNUMBER(B4),LEFT(TEXT(B4,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Di.</v>
       </c>
       <c r="B4" s="3">
@@ -988,19 +2359,35 @@
       </c>
       <c r="J4" s="10">
         <f>SUMIF(Stundenliste[Wer],I4,Stundenliste[Stunden])</f>
-        <v>0.66666666666666652</v>
+        <v>0.83333333333333326</v>
       </c>
       <c r="L4" t="s">
         <v>11</v>
       </c>
       <c r="M4" s="11">
         <f>SUM(J5,J8,J9,J11)</f>
-        <v>2.6527777777777786</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.8611111111111116</v>
+      </c>
+      <c r="N4" s="19">
+        <f t="shared" ref="N4:N5" si="2">M4</f>
+        <v>2.8611111111111116</v>
+      </c>
+      <c r="O4" s="19">
+        <f t="shared" ref="O4:O5" si="3">N4/60</f>
+        <v>4.7685185185185192E-2</v>
+      </c>
+      <c r="P4" s="23">
+        <f t="shared" si="1"/>
+        <v>2.6491769547325107E-2</v>
+      </c>
+      <c r="Q4" s="22">
+        <f t="shared" ref="Q4:Q6" si="4">(P4*1421.05263157894)/100</f>
+        <v>0.37646198830409167</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="str">
-        <f>IF(ISNUMBER(B5),LEFT(TEXT(B5,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Di.</v>
       </c>
       <c r="B5" s="3">
@@ -1034,12 +2421,28 @@
       </c>
       <c r="M5" s="11">
         <f>SUM(J3,J7,J9,J11)</f>
-        <v>3.166666666666667</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+        <v>3.375</v>
+      </c>
+      <c r="N5" s="19">
+        <f t="shared" si="2"/>
+        <v>3.375</v>
+      </c>
+      <c r="O5" s="19">
+        <f t="shared" si="3"/>
+        <v>5.6250000000000001E-2</v>
+      </c>
+      <c r="P5" s="23">
+        <f t="shared" si="1"/>
+        <v>3.125E-2</v>
+      </c>
+      <c r="Q5" s="22">
+        <f t="shared" si="4"/>
+        <v>0.44407894736841874</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="str">
-        <f>IF(ISNUMBER(B6),LEFT(TEXT(B6,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Di.</v>
       </c>
       <c r="B6" s="3">
@@ -1063,10 +2466,26 @@
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="10"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M6" s="11"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="20">
+        <v>180</v>
+      </c>
+      <c r="P6" s="21">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="Q6" s="22">
+        <f>(P6)/100</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="str">
-        <f>IF(ISNUMBER(B7),LEFT(TEXT(B7,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Di.</v>
       </c>
       <c r="B7" s="3">
@@ -1097,12 +2516,15 @@
       </c>
       <c r="M7" s="15">
         <f>SUM(F2:F41)</f>
-        <v>4.4236111111111125</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+        <v>4.7986111111111125</v>
+      </c>
+      <c r="N7">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="str">
-        <f>IF(ISNUMBER(B8),LEFT(TEXT(B8,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Sa.</v>
       </c>
       <c r="B8" s="3">
@@ -1133,12 +2555,12 @@
       </c>
       <c r="M8" s="16">
         <f>TEXT(M7,"[h]")+TEXT(M7,"mm")/60</f>
-        <v>106.16666666666667</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+        <v>115.16666666666667</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="str">
-        <f>IF(ISNUMBER(B9),LEFT(TEXT(B9,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Fr.</v>
       </c>
       <c r="B9" s="3">
@@ -1168,9 +2590,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="str">
-        <f>IF(ISNUMBER(B10),LEFT(TEXT(B10,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Sa.</v>
       </c>
       <c r="B10" s="3">
@@ -1195,9 +2617,9 @@
       <c r="I10" s="3"/>
       <c r="J10" s="10"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="str">
-        <f>IF(ISNUMBER(B11),LEFT(TEXT(B11,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Mi.</v>
       </c>
       <c r="B11" s="3">
@@ -1224,12 +2646,12 @@
       </c>
       <c r="J11" s="10">
         <f>SUMIF(Stundenliste[Wer],I11,Stundenliste[Stunden])</f>
-        <v>2.0625000000000004</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.2708333333333335</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="str">
-        <f>IF(ISNUMBER(B12),LEFT(TEXT(B12,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>So.</v>
       </c>
       <c r="B12" s="3">
@@ -1252,9 +2674,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="str">
-        <f>IF(ISNUMBER(B13),LEFT(TEXT(B13,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Fr.</v>
       </c>
       <c r="B13" s="3">
@@ -1280,9 +2702,9 @@
       <c r="J13" s="9"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="str">
-        <f>IF(ISNUMBER(B14),LEFT(TEXT(B14,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Fr.</v>
       </c>
       <c r="B14" s="3">
@@ -1308,9 +2730,9 @@
       <c r="J14" s="9"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="str">
-        <f>IF(ISNUMBER(B15),LEFT(TEXT(B15,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Sa.</v>
       </c>
       <c r="B15" s="3">
@@ -1333,9 +2755,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="str">
-        <f>IF(ISNUMBER(B16),LEFT(TEXT(B16,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Sa.</v>
       </c>
       <c r="B16" s="3">
@@ -1360,7 +2782,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="str">
-        <f>IF(ISNUMBER(B17),LEFT(TEXT(B17,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Mi.</v>
       </c>
       <c r="B17" s="3">
@@ -1385,7 +2807,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="str">
-        <f>IF(ISNUMBER(B18),LEFT(TEXT(B18,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Mi.</v>
       </c>
       <c r="B18" s="3">
@@ -1410,7 +2832,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="str">
-        <f>IF(ISNUMBER(B19),LEFT(TEXT(B19,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Do.</v>
       </c>
       <c r="B19" s="3">
@@ -1435,7 +2857,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="str">
-        <f>IF(ISNUMBER(B20),LEFT(TEXT(B20,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Fr.</v>
       </c>
       <c r="B20" s="3">
@@ -1460,7 +2882,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="str">
-        <f>IF(ISNUMBER(B21),LEFT(TEXT(B21,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Fr.</v>
       </c>
       <c r="B21" s="3">
@@ -1485,7 +2907,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="str">
-        <f>IF(ISNUMBER(B22),LEFT(TEXT(B22,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Sa.</v>
       </c>
       <c r="B22" s="3">
@@ -1510,7 +2932,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="str">
-        <f>IF(ISNUMBER(B23),LEFT(TEXT(B23,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Sa.</v>
       </c>
       <c r="B23" s="3">
@@ -1535,7 +2957,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="str">
-        <f>IF(ISNUMBER(B24),LEFT(TEXT(B24,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Fr.</v>
       </c>
       <c r="B24" s="3">
@@ -1560,7 +2982,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="str">
-        <f>IF(ISNUMBER(B25),LEFT(TEXT(B25,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Mo.</v>
       </c>
       <c r="B25" s="3">
@@ -1585,7 +3007,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="str">
-        <f>IF(ISNUMBER(B26),LEFT(TEXT(B26,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Mi.</v>
       </c>
       <c r="B26" s="3">
@@ -1610,7 +3032,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="str">
-        <f>IF(ISNUMBER(B27),LEFT(TEXT(B27,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Mi.</v>
       </c>
       <c r="B27" s="3">
@@ -1635,7 +3057,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="str">
-        <f>IF(ISNUMBER(B28),LEFT(TEXT(B28,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Mi.</v>
       </c>
       <c r="B28" s="3">
@@ -1660,7 +3082,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="str">
-        <f>IF(ISNUMBER(B29),LEFT(TEXT(B29,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Mo.</v>
       </c>
       <c r="B29" s="3">
@@ -1685,7 +3107,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="str">
-        <f>IF(ISNUMBER(B30),LEFT(TEXT(B30,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Mo.</v>
       </c>
       <c r="B30" s="3">
@@ -1710,7 +3132,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="str">
-        <f>IF(ISNUMBER(B31),LEFT(TEXT(B31,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Fr.</v>
       </c>
       <c r="B31" s="3">
@@ -1735,7 +3157,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="str">
-        <f>IF(ISNUMBER(B32),LEFT(TEXT(B32,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Fr.</v>
       </c>
       <c r="B32" s="3">
@@ -1760,7 +3182,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="str">
-        <f>IF(ISNUMBER(B33),LEFT(TEXT(B33,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Mo.</v>
       </c>
       <c r="B33" s="3">
@@ -1785,7 +3207,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="str">
-        <f>IF(ISNUMBER(B34),LEFT(TEXT(B34,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Mo.</v>
       </c>
       <c r="B34" s="3">
@@ -1809,59 +3231,108 @@
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="17"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="2"/>
+      <c r="A35" s="17" t="str">
+        <f t="shared" ref="A35:A41" si="5">IF(ISNUMBER(B35),LEFT(TEXT(B35,"TTTT"),2)&amp;".","")</f>
+        <v>Fr.</v>
+      </c>
+      <c r="B35" s="3">
+        <v>46024</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E35" s="4">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F35" s="12">
+        <f>IF(E35&gt;D35,E35-D35,IF(ISNUMBER([1]!Stundenliste[[#This Row],[Von]]),"24:00"-(D35-E35),""))</f>
+        <v>8.333333333333337E-2</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="17" t="str">
-        <f>IF(ISNUMBER(B36),LEFT(TEXT(B36,"TTTT"),2)&amp;".","")</f>
-        <v/>
-      </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="2"/>
+        <f t="shared" si="5"/>
+        <v>Sa.</v>
+      </c>
+      <c r="B36" s="3">
+        <v>46025</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D36" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E36" s="4">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F36" s="12">
+        <f>IF(E36&gt;D36,E36-D36,IF(ISNUMBER([1]!Stundenliste[[#This Row],[Von]]),"24:00"-(D36-E36),""))</f>
+        <v>8.333333333333337E-2</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="17" t="str">
-        <f>IF(ISNUMBER(B37),LEFT(TEXT(B37,"TTTT"),2)&amp;".","")</f>
-        <v/>
-      </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="12" t="str">
+        <f t="shared" si="5"/>
+        <v>So.</v>
+      </c>
+      <c r="B37" s="3">
+        <v>46026</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D37" s="4">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="E37" s="4">
+        <v>0.875</v>
+      </c>
+      <c r="F37" s="12">
         <f>IF(E37&gt;D37,E37-D37,IF(ISNUMBER([1]!Stundenliste[[#This Row],[Von]]),"24:00"-(D37-E37),""))</f>
-        <v/>
-      </c>
-      <c r="G37" s="2"/>
+        <v>0.16666666666666663</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="17" t="str">
-        <f>IF(ISNUMBER(B38),LEFT(TEXT(B38,"TTTT"),2)&amp;".","")</f>
-        <v/>
-      </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="12" t="str">
+        <f t="shared" si="5"/>
+        <v>Fr.</v>
+      </c>
+      <c r="B38" s="3">
+        <v>46031</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D38" s="4">
+        <v>0.30902777777777779</v>
+      </c>
+      <c r="E38" s="4">
+        <v>0.35069444444444442</v>
+      </c>
+      <c r="F38" s="12">
         <f>IF(E38&gt;D38,E38-D38,IF(ISNUMBER([1]!Stundenliste[[#This Row],[Von]]),"24:00"-(D38-E38),""))</f>
-        <v/>
-      </c>
-      <c r="G38" s="2"/>
+        <v>4.166666666666663E-2</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="17" t="str">
-        <f>IF(ISNUMBER(B39),LEFT(TEXT(B39,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="B39" s="3"/>
@@ -1876,7 +3347,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="17" t="str">
-        <f>IF(ISNUMBER(B40),LEFT(TEXT(B40,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="B40" s="3"/>
@@ -1891,7 +3362,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="17" t="str">
-        <f>IF(ISNUMBER(B41),LEFT(TEXT(B41,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="B41" s="3"/>
@@ -1907,15 +3378,33 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <tableParts count="3">
-    <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <ReferenceId xmlns="d9f85066-e658-4e34-914c-f198c2427564" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101001F6A9684FA57F34CA0CFF8DECC7C89F4" ma:contentTypeVersion="4" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="b2ec2b65d3d5b16c44b9b6a36409c0c6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d9f85066-e658-4e34-914c-f198c2427564" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5b8d1bb51b8c1f0753974a44edfe3f74" ns2:_="">
     <xsd:import namespace="d9f85066-e658-4e34-914c-f198c2427564"/>
@@ -2059,42 +3548,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <ReferenceId xmlns="d9f85066-e658-4e34-914c-f198c2427564" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834A42BE-934C-42D8-9F79-C190EDC62F20}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="d9f85066-e658-4e34-914c-f198c2427564"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57E083A2-B59E-4178-BBDB-6F72551558F7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -2112,10 +3566,28 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A879EED-63D4-4BD6-ABDC-8DEB19CAAEDF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834A42BE-934C-42D8-9F79-C190EDC62F20}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d9f85066-e658-4e34-914c-f198c2427564"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Stundenliste(1).xlsx
+++ b/Stundenliste(1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linus.pilz\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anwender\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7892893B-8816-4356-95B0-22028287196E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD32268D-1533-45B2-81E9-02A095F5C2DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{904973F5-B02B-4666-A03D-BB66738E721E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{904973F5-B02B-4666-A03D-BB66738E721E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -34,15 +34,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="53">
   <si>
     <t>Tag</t>
   </si>
@@ -192,6 +189,15 @@
   </si>
   <si>
     <t>Spalte1</t>
+  </si>
+  <si>
+    <t>Vr-Brillen und Meta reaperieren + Standalone</t>
+  </si>
+  <si>
+    <t>Fehlerbehben (Debugging)</t>
+  </si>
+  <si>
+    <t>Programmiert</t>
   </si>
 </sst>
 </file>
@@ -291,7 +297,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -319,7 +325,6 @@
     <xf numFmtId="168" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="46" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -332,21 +337,6 @@
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="17">
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="[mm]"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="[mm]"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[hh]:mm"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -402,6 +392,21 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[mm]"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[mm]"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[hh]:mm"/>
     </dxf>
     <dxf>
       <font>
@@ -708,7 +713,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.54002192982455854</c:v>
+                  <c:v>0.58936403508771606</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -808,7 +813,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.37646198830409167</c:v>
+                  <c:v>0.39839181286549502</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -908,7 +913,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.44407894736841874</c:v>
+                  <c:v>0.46600877192982215</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1861,17 +1866,17 @@
   <autoFilter ref="L2:Q6" xr:uid="{028D3482-62D4-45D7-85FA-8EC2E4DDD78D}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9B6AAEA3-668A-4353-A33E-0D79279FD064}" name="Name"/>
-    <tableColumn id="2" xr3:uid="{DF593358-143C-4B61-887F-2E7A8967BB61}" name="Stunden" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{48C02AA9-4970-411A-A4BA-20AFF4C20E61}" name="Minuten" dataDxfId="3">
+    <tableColumn id="2" xr3:uid="{DF593358-143C-4B61-887F-2E7A8967BB61}" name="Stunden" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{48C02AA9-4970-411A-A4BA-20AFF4C20E61}" name="Minuten" dataDxfId="6">
       <calculatedColumnFormula>Tabelle2[[#This Row],[Stunden]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{FBD2B55A-1785-4AEE-A362-0CDA5F4271CA}" name="Stunden2" dataDxfId="2">
+    <tableColumn id="4" xr3:uid="{FBD2B55A-1785-4AEE-A362-0CDA5F4271CA}" name="Stunden2" dataDxfId="5">
       <calculatedColumnFormula>Tabelle2[[#This Row],[Minuten]]/60</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{43C88CC5-3A35-4698-8EA5-94C339438E12}" name="Prozent" dataDxfId="1">
+    <tableColumn id="5" xr3:uid="{43C88CC5-3A35-4698-8EA5-94C339438E12}" name="Prozent" dataDxfId="4">
       <calculatedColumnFormula>(O3/180)*100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{6AA6588C-B2BB-4A64-8166-D31634AA0806}" name="Spalte1" dataDxfId="0">
+    <tableColumn id="6" xr3:uid="{6AA6588C-B2BB-4A64-8166-D31634AA0806}" name="Spalte1" dataDxfId="3">
       <calculatedColumnFormula>P3*1421.05263157894</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1880,11 +1885,11 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8B5F2195-23C3-4CB7-A5D3-21B8075D8571}" name="Tabelle5" displayName="Tabelle5" ref="I2:J11" totalsRowShown="0" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8B5F2195-23C3-4CB7-A5D3-21B8075D8571}" name="Tabelle5" displayName="Tabelle5" ref="I2:J11" totalsRowShown="0" dataDxfId="2">
   <autoFilter ref="I2:J11" xr:uid="{8B5F2195-23C3-4CB7-A5D3-21B8075D8571}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{5F655F81-B105-43EE-8AB9-3B34703E1464}" name="Name" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{B0F8400B-CC18-431B-B826-95EE145FC5C8}" name="Zeit" dataDxfId="5">
+    <tableColumn id="1" xr3:uid="{5F655F81-B105-43EE-8AB9-3B34703E1464}" name="Name" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{B0F8400B-CC18-431B-B826-95EE145FC5C8}" name="Zeit" dataDxfId="0">
       <calculatedColumnFormula>SUMIF(Stundenliste[Wer],I3,Stundenliste[Stunden])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2311,23 +2316,23 @@
       </c>
       <c r="M3" s="11">
         <f>SUM(J4,J7,J8,J11)</f>
-        <v>4.1041666666666661</v>
-      </c>
-      <c r="N3" s="19">
+        <v>4.4791666666666661</v>
+      </c>
+      <c r="N3" s="18">
         <f>M3</f>
-        <v>4.1041666666666661</v>
-      </c>
-      <c r="O3" s="19">
+        <v>4.4791666666666661</v>
+      </c>
+      <c r="O3" s="18">
         <f>N3/60</f>
-        <v>6.8402777777777771E-2</v>
-      </c>
-      <c r="P3" s="23">
+        <v>7.4652777777777762E-2</v>
+      </c>
+      <c r="P3" s="22">
         <f t="shared" ref="P3:P6" si="1">(O3/180)*100</f>
-        <v>3.8001543209876538E-2</v>
-      </c>
-      <c r="Q3" s="22">
+        <v>4.1473765432098755E-2</v>
+      </c>
+      <c r="Q3" s="21">
         <f>(P3*1421.05263157894)/100</f>
-        <v>0.54002192982455854</v>
+        <v>0.58936403508771606</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -2359,30 +2364,30 @@
       </c>
       <c r="J4" s="10">
         <f>SUMIF(Stundenliste[Wer],I4,Stundenliste[Stunden])</f>
-        <v>0.83333333333333326</v>
+        <v>1.0416666666666665</v>
       </c>
       <c r="L4" t="s">
         <v>11</v>
       </c>
       <c r="M4" s="11">
         <f>SUM(J5,J8,J9,J11)</f>
-        <v>2.8611111111111116</v>
-      </c>
-      <c r="N4" s="19">
+        <v>3.0277777777777781</v>
+      </c>
+      <c r="N4" s="18">
         <f t="shared" ref="N4:N5" si="2">M4</f>
-        <v>2.8611111111111116</v>
-      </c>
-      <c r="O4" s="19">
+        <v>3.0277777777777781</v>
+      </c>
+      <c r="O4" s="18">
         <f t="shared" ref="O4:O5" si="3">N4/60</f>
-        <v>4.7685185185185192E-2</v>
-      </c>
-      <c r="P4" s="23">
+        <v>5.0462962962962966E-2</v>
+      </c>
+      <c r="P4" s="22">
         <f t="shared" si="1"/>
-        <v>2.6491769547325107E-2</v>
-      </c>
-      <c r="Q4" s="22">
-        <f t="shared" ref="Q4:Q6" si="4">(P4*1421.05263157894)/100</f>
-        <v>0.37646198830409167</v>
+        <v>2.8034979423868317E-2</v>
+      </c>
+      <c r="Q4" s="21">
+        <f t="shared" ref="Q4:Q5" si="4">(P4*1421.05263157894)/100</f>
+        <v>0.39839181286549502</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -2421,23 +2426,23 @@
       </c>
       <c r="M5" s="11">
         <f>SUM(J3,J7,J9,J11)</f>
-        <v>3.375</v>
-      </c>
-      <c r="N5" s="19">
+        <v>3.5416666666666665</v>
+      </c>
+      <c r="N5" s="18">
         <f t="shared" si="2"/>
-        <v>3.375</v>
-      </c>
-      <c r="O5" s="19">
+        <v>3.5416666666666665</v>
+      </c>
+      <c r="O5" s="18">
         <f t="shared" si="3"/>
-        <v>5.6250000000000001E-2</v>
-      </c>
-      <c r="P5" s="23">
+        <v>5.9027777777777776E-2</v>
+      </c>
+      <c r="P5" s="22">
         <f t="shared" si="1"/>
-        <v>3.125E-2</v>
-      </c>
-      <c r="Q5" s="22">
+        <v>3.279320987654321E-2</v>
+      </c>
+      <c r="Q5" s="21">
         <f t="shared" si="4"/>
-        <v>0.44407894736841874</v>
+        <v>0.46600877192982215</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -2470,28 +2475,28 @@
         <v>48</v>
       </c>
       <c r="M6" s="11"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="20">
+      <c r="N6" s="18"/>
+      <c r="O6" s="19">
         <v>180</v>
       </c>
-      <c r="P6" s="21">
+      <c r="P6" s="20">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="Q6" s="22">
+      <c r="Q6" s="21">
         <f>(P6)/100</f>
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="str">
+      <c r="A7" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Di.</v>
       </c>
       <c r="B7" s="3">
         <v>45881</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D7" s="4">
@@ -2516,7 +2521,7 @@
       </c>
       <c r="M7" s="15">
         <f>SUM(F2:F41)</f>
-        <v>4.7986111111111125</v>
+        <v>5.1736111111111134</v>
       </c>
       <c r="N7">
         <v>180</v>
@@ -2555,7 +2560,7 @@
       </c>
       <c r="M8" s="16">
         <f>TEXT(M7,"[h]")+TEXT(M7,"mm")/60</f>
-        <v>115.16666666666667</v>
+        <v>124.16666666666667</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -2646,7 +2651,7 @@
       </c>
       <c r="J11" s="10">
         <f>SUMIF(Stundenliste[Wer],I11,Stundenliste[Stunden])</f>
-        <v>2.2708333333333335</v>
+        <v>2.4375</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -2675,14 +2680,14 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="str">
+      <c r="A13" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Fr.</v>
       </c>
       <c r="B13" s="3">
         <v>45940</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D13" s="4">
@@ -2703,14 +2708,14 @@
       <c r="K13" s="2"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="str">
+      <c r="A14" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Fr.</v>
       </c>
       <c r="B14" s="3">
         <v>45968</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D14" s="4">
@@ -2756,14 +2761,14 @@
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="str">
+      <c r="A16" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Sa.</v>
       </c>
       <c r="B16" s="3">
         <v>45969</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D16" s="4">
@@ -2781,14 +2786,14 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="str">
+      <c r="A17" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mi.</v>
       </c>
       <c r="B17" s="3">
         <v>45973</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D17" s="4">
@@ -2806,14 +2811,14 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="str">
+      <c r="A18" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mi.</v>
       </c>
       <c r="B18" s="3">
         <v>45980</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D18" s="4">
@@ -2831,14 +2836,14 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="str">
+      <c r="A19" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Do.</v>
       </c>
       <c r="B19" s="3">
         <v>45981</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D19" s="4">
@@ -2856,14 +2861,14 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="str">
+      <c r="A20" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Fr.</v>
       </c>
       <c r="B20" s="3">
         <v>45982</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D20" s="4">
@@ -2881,14 +2886,14 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="17" t="str">
+      <c r="A21" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Fr.</v>
       </c>
       <c r="B21" s="3">
         <v>45982</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="2" t="s">
         <v>40</v>
       </c>
       <c r="D21" s="4">
@@ -2906,14 +2911,14 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="17" t="str">
+      <c r="A22" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Sa.</v>
       </c>
       <c r="B22" s="3">
         <v>45983</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D22" s="4">
@@ -2931,20 +2936,20 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="str">
+      <c r="A23" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Sa.</v>
       </c>
       <c r="B23" s="3">
         <v>45990</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D23" s="4">
         <v>0.83333333333333337</v>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="17">
         <v>1</v>
       </c>
       <c r="F23" s="12">
@@ -2981,14 +2986,14 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="str">
+      <c r="A25" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mo.</v>
       </c>
       <c r="B25" s="3">
         <v>45999</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D25" s="4">
@@ -3056,14 +3061,14 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="str">
+      <c r="A28" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mi.</v>
       </c>
       <c r="B28" s="3">
         <v>46001</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D28" s="4">
@@ -3081,14 +3086,14 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="str">
+      <c r="A29" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mo.</v>
       </c>
       <c r="B29" s="3">
         <v>46013</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D29" s="4">
@@ -3106,14 +3111,14 @@
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="17" t="str">
+      <c r="A30" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mo.</v>
       </c>
       <c r="B30" s="3">
         <v>46013</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C30" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D30" s="4">
@@ -3131,14 +3136,14 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="str">
+      <c r="A31" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Fr.</v>
       </c>
       <c r="B31" s="3">
         <v>46017</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D31" s="4">
@@ -3156,14 +3161,14 @@
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="17" t="str">
+      <c r="A32" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Fr.</v>
       </c>
       <c r="B32" s="3">
         <v>46017</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="4">
@@ -3181,14 +3186,14 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="17" t="str">
+      <c r="A33" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mo.</v>
       </c>
       <c r="B33" s="3">
         <v>46020</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D33" s="4">
@@ -3206,14 +3211,14 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="17" t="str">
+      <c r="A34" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mo.</v>
       </c>
       <c r="B34" s="3">
         <v>46020</v>
       </c>
-      <c r="C34" s="17" t="s">
+      <c r="C34" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D34" s="4">
@@ -3231,14 +3236,14 @@
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="17" t="str">
+      <c r="A35" s="2" t="str">
         <f t="shared" ref="A35:A41" si="5">IF(ISNUMBER(B35),LEFT(TEXT(B35,"TTTT"),2)&amp;".","")</f>
         <v>Fr.</v>
       </c>
       <c r="B35" s="3">
         <v>46024</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="2" t="s">
         <v>44</v>
       </c>
       <c r="D35" s="4">
@@ -3256,14 +3261,14 @@
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="17" t="str">
+      <c r="A36" s="2" t="str">
         <f t="shared" si="5"/>
         <v>Sa.</v>
       </c>
       <c r="B36" s="3">
         <v>46025</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C36" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D36" s="4">
@@ -3281,14 +3286,14 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="17" t="str">
+      <c r="A37" s="2" t="str">
         <f t="shared" si="5"/>
         <v>So.</v>
       </c>
       <c r="B37" s="3">
         <v>46026</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="2" t="s">
         <v>46</v>
       </c>
       <c r="D37" s="4">
@@ -3306,14 +3311,14 @@
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="17" t="str">
+      <c r="A38" s="2" t="str">
         <f t="shared" si="5"/>
         <v>Fr.</v>
       </c>
       <c r="B38" s="3">
         <v>46031</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="C38" s="2" t="s">
         <v>47</v>
       </c>
       <c r="D38" s="4">
@@ -3331,49 +3336,79 @@
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="17" t="str">
+      <c r="A39" s="2" t="str">
+        <f>IF(ISNUMBER(B39),LEFT(TEXT(B39,"TTTT"),2)&amp;".","")</f>
+        <v>Mi.</v>
+      </c>
+      <c r="B39" s="3">
+        <v>46050</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D39" s="4">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="E39" s="4">
+        <v>0.76388888888888884</v>
+      </c>
+      <c r="F39" s="12">
+        <f>IF(E39&gt;D39,E39-D39,IF(ISNUMBER([1]!Stundenliste[[#This Row],[Von]]),"24:00"-(D39-E39),""))</f>
+        <v>4.166666666666663E-2</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="12" t="str">
-        <f>IF(E39&gt;D39,E39-D39,IF(ISNUMBER([1]!Stundenliste[[#This Row],[Von]]),"24:00"-(D39-E39),""))</f>
-        <v/>
-      </c>
-      <c r="G39" s="2"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="17" t="str">
+        <v>Fr.</v>
+      </c>
+      <c r="B40" s="3">
+        <v>46038</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D40" s="4">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E40" s="4">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F40" s="12">
+        <f>IF(E40&gt;D40,E40-D40,IF(ISNUMBER([1]!Stundenliste[[#This Row],[Von]]),"24:00"-(D40-E40),""))</f>
+        <v>0.16666666666666674</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="B40" s="3"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="12" t="str">
-        <f>IF(E40&gt;D40,E40-D40,IF(ISNUMBER([1]!Stundenliste[[#This Row],[Von]]),"24:00"-(D40-E40),""))</f>
-        <v/>
-      </c>
-      <c r="G40" s="2"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="17" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="12" t="str">
+        <v>Sa.</v>
+      </c>
+      <c r="B41" s="3">
+        <v>46039</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D41" s="4">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E41" s="4">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F41" s="12">
         <f>IF(E41&gt;D41,E41-D41,IF(ISNUMBER([1]!Stundenliste[[#This Row],[Von]]),"24:00"-(D41-E41),""))</f>
-        <v/>
-      </c>
-      <c r="G41" s="2"/>
+        <v>0.16666666666666674</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -3388,23 +3423,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <ReferenceId xmlns="d9f85066-e658-4e34-914c-f198c2427564" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101001F6A9684FA57F34CA0CFF8DECC7C89F4" ma:contentTypeVersion="4" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="b2ec2b65d3d5b16c44b9b6a36409c0c6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d9f85066-e658-4e34-914c-f198c2427564" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5b8d1bb51b8c1f0753974a44edfe3f74" ns2:_="">
     <xsd:import namespace="d9f85066-e658-4e34-914c-f198c2427564"/>
@@ -3548,7 +3566,50 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <ReferenceId xmlns="d9f85066-e658-4e34-914c-f198c2427564" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834A42BE-934C-42D8-9F79-C190EDC62F20}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d9f85066-e658-4e34-914c-f198c2427564"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A879EED-63D4-4BD6-ABDC-8DEB19CAAEDF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57E083A2-B59E-4178-BBDB-6F72551558F7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -3564,30 +3625,4 @@
     <ds:schemaRef ds:uri="d9f85066-e658-4e34-914c-f198c2427564"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A879EED-63D4-4BD6-ABDC-8DEB19CAAEDF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834A42BE-934C-42D8-9F79-C190EDC62F20}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="d9f85066-e658-4e34-914c-f198c2427564"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Stundenliste(1).xlsx
+++ b/Stundenliste(1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anwender\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linus\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD32268D-1533-45B2-81E9-02A095F5C2DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B36D607E-EB71-4EB3-8367-863CBA016A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{904973F5-B02B-4666-A03D-BB66738E721E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{904973F5-B02B-4666-A03D-BB66738E721E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="55">
   <si>
     <t>Tag</t>
   </si>
@@ -198,6 +198,12 @@
   </si>
   <si>
     <t>Programmiert</t>
+  </si>
+  <si>
+    <t>Inno Esa Wettbewerb</t>
+  </si>
+  <si>
+    <t>Word weitergeschrieben und verbessert</t>
   </si>
 </sst>
 </file>
@@ -297,7 +303,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -331,6 +337,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Prozent" xfId="1" builtinId="5"/>
@@ -713,7 +720,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.58936403508771606</c:v>
+                  <c:v>0.61129385964911986</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1839,8 +1846,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD71F5EC-BCBD-4D95-9F21-060EF7779827}" name="Stundenliste" displayName="Stundenliste" ref="A1:G41" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A1:G41" xr:uid="{730AE997-56E9-481C-8C9C-45C7D9E3EFFC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD71F5EC-BCBD-4D95-9F21-060EF7779827}" name="Stundenliste" displayName="Stundenliste" ref="A1:G43" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:G43" xr:uid="{730AE997-56E9-481C-8C9C-45C7D9E3EFFC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G41">
     <sortCondition ref="B1:B41"/>
   </sortState>
@@ -2195,19 +2202,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{730198CE-52B5-4F02-9B4B-1774B163D30B}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="A1:Q41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q43"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" customWidth="1"/>
-    <col min="3" max="3" width="30.5703125" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" customWidth="1"/>
-    <col min="5" max="5" width="8.28515625" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" customWidth="1"/>
+    <col min="3" max="3" width="30.5546875" customWidth="1"/>
+    <col min="4" max="4" width="9.44140625" customWidth="1"/>
+    <col min="5" max="5" width="8.33203125" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2230,7 +2237,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="str">
         <f t="shared" ref="A2:A34" si="0">IF(ISNUMBER(B2),LEFT(TEXT(B2,"TTTT"),2)&amp;".","")</f>
         <v>So.</v>
@@ -2279,7 +2286,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Di.</v>
@@ -2316,26 +2323,26 @@
       </c>
       <c r="M3" s="11">
         <f>SUM(J4,J7,J8,J11)</f>
-        <v>4.4791666666666661</v>
+        <v>4.6458333333333339</v>
       </c>
       <c r="N3" s="18">
         <f>M3</f>
-        <v>4.4791666666666661</v>
+        <v>4.6458333333333339</v>
       </c>
       <c r="O3" s="18">
         <f>N3/60</f>
-        <v>7.4652777777777762E-2</v>
+        <v>7.7430555555555572E-2</v>
       </c>
       <c r="P3" s="22">
         <f t="shared" ref="P3:P6" si="1">(O3/180)*100</f>
-        <v>4.1473765432098755E-2</v>
+        <v>4.3016975308641986E-2</v>
       </c>
       <c r="Q3" s="21">
         <f>(P3*1421.05263157894)/100</f>
-        <v>0.58936403508771606</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.61129385964911986</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Di.</v>
@@ -2364,7 +2371,7 @@
       </c>
       <c r="J4" s="10">
         <f>SUMIF(Stundenliste[Wer],I4,Stundenliste[Stunden])</f>
-        <v>1.0416666666666665</v>
+        <v>1.2083333333333335</v>
       </c>
       <c r="L4" t="s">
         <v>11</v>
@@ -2390,7 +2397,7 @@
         <v>0.39839181286549502</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Di.</v>
@@ -2445,7 +2452,7 @@
         <v>0.46600877192982215</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Di.</v>
@@ -2488,7 +2495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Di.</v>
@@ -2520,14 +2527,14 @@
         <v>0.49999999999999989</v>
       </c>
       <c r="M7" s="15">
-        <f>SUM(F2:F41)</f>
-        <v>5.1736111111111134</v>
+        <f>SUM(F2:F43)</f>
+        <v>5.3402777777777795</v>
       </c>
       <c r="N7">
         <v>180</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Sa.</v>
@@ -2560,10 +2567,10 @@
       </c>
       <c r="M8" s="16">
         <f>TEXT(M7,"[h]")+TEXT(M7,"mm")/60</f>
-        <v>124.16666666666667</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+        <v>128.16666666666666</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Fr.</v>
@@ -2595,7 +2602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Sa.</v>
@@ -2622,7 +2629,7 @@
       <c r="I10" s="3"/>
       <c r="J10" s="10"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mi.</v>
@@ -2654,7 +2661,7 @@
         <v>2.4375</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="str">
         <f t="shared" si="0"/>
         <v>So.</v>
@@ -2679,7 +2686,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Fr.</v>
@@ -2707,7 +2714,7 @@
       <c r="J13" s="9"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Fr.</v>
@@ -2735,7 +2742,7 @@
       <c r="J14" s="9"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Sa.</v>
@@ -2760,7 +2767,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Sa.</v>
@@ -2785,7 +2792,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mi.</v>
@@ -2810,7 +2817,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mi.</v>
@@ -2835,7 +2842,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Do.</v>
@@ -2860,7 +2867,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Fr.</v>
@@ -2885,7 +2892,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Fr.</v>
@@ -2910,7 +2917,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Sa.</v>
@@ -2935,7 +2942,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Sa.</v>
@@ -2960,7 +2967,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Fr.</v>
@@ -2985,7 +2992,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mo.</v>
@@ -3010,7 +3017,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mi.</v>
@@ -3035,7 +3042,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mi.</v>
@@ -3060,7 +3067,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mi.</v>
@@ -3085,7 +3092,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mo.</v>
@@ -3110,7 +3117,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mo.</v>
@@ -3135,7 +3142,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Fr.</v>
@@ -3160,7 +3167,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Fr.</v>
@@ -3185,7 +3192,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mo.</v>
@@ -3210,7 +3217,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mo.</v>
@@ -3235,7 +3242,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="str">
         <f t="shared" ref="A35:A41" si="5">IF(ISNUMBER(B35),LEFT(TEXT(B35,"TTTT"),2)&amp;".","")</f>
         <v>Fr.</v>
@@ -3260,7 +3267,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="str">
         <f t="shared" si="5"/>
         <v>Sa.</v>
@@ -3285,7 +3292,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="str">
         <f t="shared" si="5"/>
         <v>So.</v>
@@ -3310,7 +3317,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="str">
         <f t="shared" si="5"/>
         <v>Fr.</v>
@@ -3335,7 +3342,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="str">
         <f>IF(ISNUMBER(B39),LEFT(TEXT(B39,"TTTT"),2)&amp;".","")</f>
         <v>Mi.</v>
@@ -3360,7 +3367,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="str">
         <f t="shared" si="5"/>
         <v>Fr.</v>
@@ -3385,7 +3392,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="str">
         <f t="shared" si="5"/>
         <v>Sa.</v>
@@ -3407,6 +3414,56 @@
         <v>0.16666666666666674</v>
       </c>
       <c r="G41" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="23" t="str">
+        <f>IF(ISNUMBER(B42),LEFT(TEXT(B42,"TTTT"),2)&amp;".","")</f>
+        <v>Di.</v>
+      </c>
+      <c r="B42" s="3">
+        <v>46042</v>
+      </c>
+      <c r="C42" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="D42" s="4">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="E42" s="17">
+        <v>1</v>
+      </c>
+      <c r="F42" s="12">
+        <f>IF(E42&gt;D42,E42-D42,IF(ISNUMBER([1]!Stundenliste[[#This Row],[Von]]),"24:00"-(D42-E42),""))</f>
+        <v>8.333333333333337E-2</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="23" t="str">
+        <f>IF(ISNUMBER(B43),LEFT(TEXT(B43,"TTTT"),2)&amp;".","")</f>
+        <v>Mi.</v>
+      </c>
+      <c r="B43" s="3">
+        <v>46057</v>
+      </c>
+      <c r="C43" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D43" s="4">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="E43" s="17">
+        <v>1</v>
+      </c>
+      <c r="F43" s="12">
+        <f>IF(E43&gt;D43,E43-D43,IF(ISNUMBER([1]!Stundenliste[[#This Row],[Von]]),"24:00"-(D43-E43),""))</f>
+        <v>8.333333333333337E-2</v>
+      </c>
+      <c r="G43" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3423,6 +3480,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <ReferenceId xmlns="d9f85066-e658-4e34-914c-f198c2427564" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101001F6A9684FA57F34CA0CFF8DECC7C89F4" ma:contentTypeVersion="4" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="b2ec2b65d3d5b16c44b9b6a36409c0c6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d9f85066-e658-4e34-914c-f198c2427564" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5b8d1bb51b8c1f0753974a44edfe3f74" ns2:_="">
     <xsd:import namespace="d9f85066-e658-4e34-914c-f198c2427564"/>
@@ -3566,24 +3640,33 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57E083A2-B59E-4178-BBDB-6F72551558F7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="33483e06-99ee-4919-8fc9-f487e9b68a5e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="becce21f-4543-4ee3-84d8-746b4cf7c34b"/>
+    <ds:schemaRef ds:uri="d9f85066-e658-4e34-914c-f198c2427564"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <ReferenceId xmlns="d9f85066-e658-4e34-914c-f198c2427564" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A879EED-63D4-4BD6-ABDC-8DEB19CAAEDF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834A42BE-934C-42D8-9F79-C190EDC62F20}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3599,30 +3682,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A879EED-63D4-4BD6-ABDC-8DEB19CAAEDF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57E083A2-B59E-4178-BBDB-6F72551558F7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="33483e06-99ee-4919-8fc9-f487e9b68a5e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="becce21f-4543-4ee3-84d8-746b4cf7c34b"/>
-    <ds:schemaRef ds:uri="d9f85066-e658-4e34-914c-f198c2427564"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>